--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7326" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7328" uniqueCount="727">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -499,7 +499,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -533,7 +533,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -576,7 +576,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -611,6 +611,10 @@
     <t>Medication.contained</t>
   </si>
   <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -627,6 +631,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Medication.extension</t>
   </si>
   <si>
@@ -634,9 +641,6 @@
   </si>
   <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -663,6 +667,9 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-id-vaccine-extension}
 </t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>Indicator of whether this is a vaccine.</t>
@@ -916,9 +923,6 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
@@ -1078,10 +1082,10 @@
 </t>
   </si>
   <si>
-    <t>Business identifier for this medication</t>
-  </si>
-  <si>
-    <t>Business identifier for this medication.</t>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
   </si>
   <si>
     <t>The serial number could be included as an identifier.</t>
@@ -1126,7 +1130,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1346,7 +1350,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1416,7 +1420,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1473,7 +1477,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1923,7 +1927,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
+Reference(Substance|Medication)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -2602,7 +2606,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4477,7 +4481,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4496,16 +4500,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4555,7 +4559,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4570,10 +4574,10 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>85</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4584,10 +4588,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4616,7 +4620,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -4669,7 +4673,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4687,7 +4691,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4698,16 +4702,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4726,15 +4730,17 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4783,7 +4789,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4792,7 +4798,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4801,7 +4807,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4812,13 +4818,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4840,13 +4846,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4897,7 +4903,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4906,7 +4912,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -4915,7 +4921,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4926,10 +4932,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5038,10 +5044,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5067,10 +5073,10 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5150,10 +5156,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5179,13 +5185,13 @@
         <v>129</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5193,7 +5199,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>77</v>
@@ -5235,7 +5241,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -5253,7 +5259,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -5264,10 +5270,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5290,13 +5296,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5347,7 +5353,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5365,7 +5371,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -5376,13 +5382,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>77</v>
@@ -5404,13 +5410,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5461,7 +5467,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5470,7 +5476,7 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>116</v>
@@ -5479,7 +5485,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5490,10 +5496,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5602,10 +5608,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5631,10 +5637,10 @@
         <v>108</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5714,10 +5720,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5743,13 +5749,13 @@
         <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5757,7 +5763,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
@@ -5799,7 +5805,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>87</v>
@@ -5817,7 +5823,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5828,10 +5834,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5857,10 +5863,10 @@
         <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5887,11 +5893,11 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5909,7 +5915,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5927,7 +5933,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5938,10 +5944,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6050,10 +6056,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6164,10 +6170,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6193,16 +6199,16 @@
         <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6251,7 +6257,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6269,21 +6275,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6309,13 +6315,13 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6365,7 +6371,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6383,21 +6389,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6423,14 +6429,14 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6479,7 +6485,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6497,21 +6503,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6537,16 +6543,16 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6595,7 +6601,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6613,21 +6619,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6650,19 +6656,19 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6711,7 +6717,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6729,24 +6735,24 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6768,13 +6774,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6825,7 +6831,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6834,7 +6840,7 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>116</v>
@@ -6843,7 +6849,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6854,10 +6860,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6966,10 +6972,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7080,10 +7086,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7109,13 +7115,13 @@
         <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7123,7 +7129,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
@@ -7165,7 +7171,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -7183,7 +7189,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7194,10 +7200,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7223,10 +7229,10 @@
         <v>172</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7253,11 +7259,11 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -7275,7 +7281,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7293,7 +7299,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -7304,13 +7310,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>77</v>
@@ -7332,13 +7338,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7389,7 +7395,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7398,7 +7404,7 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>116</v>
@@ -7407,7 +7413,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7418,10 +7424,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7530,10 +7536,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7559,10 +7565,10 @@
         <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7642,10 +7648,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7671,13 +7677,13 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7685,7 +7691,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>77</v>
@@ -7727,7 +7733,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7745,7 +7751,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7756,10 +7762,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7785,10 +7791,10 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7812,7 +7818,7 @@
         <v>77</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="X46" t="s" s="2">
         <v>77</v>
@@ -7839,7 +7845,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7857,7 +7863,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7868,13 +7874,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7896,13 +7902,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7953,7 +7959,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7962,7 +7968,7 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>116</v>
@@ -7971,7 +7977,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7982,10 +7988,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8094,10 +8100,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8123,10 +8129,10 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8206,10 +8212,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8235,13 +8241,13 @@
         <v>129</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8249,7 +8255,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -8291,7 +8297,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -8309,7 +8315,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8320,10 +8326,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8349,10 +8355,10 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8376,7 +8382,7 @@
         <v>77</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="X51" t="s" s="2">
         <v>77</v>
@@ -8403,7 +8409,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8421,7 +8427,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8432,16 +8438,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8460,15 +8466,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8517,7 +8525,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8526,7 +8534,7 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>116</v>
@@ -8535,7 +8543,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8546,10 +8554,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8575,16 +8583,16 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8633,7 +8641,7 @@
         <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8651,7 +8659,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8662,10 +8670,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8688,16 +8696,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8745,7 +8753,7 @@
         <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8763,24 +8771,24 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8802,16 +8810,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8822,7 +8830,7 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>77</v>
@@ -8861,7 +8869,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8879,24 +8887,24 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8918,16 +8926,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8938,7 +8946,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8977,7 +8985,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8995,21 +9003,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9032,16 +9040,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9070,10 +9078,10 @@
         <v>162</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -9091,7 +9099,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9106,24 +9114,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9232,10 +9240,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9346,10 +9354,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9375,16 +9383,16 @@
         <v>147</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9431,7 +9439,7 @@
         <v>114</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9449,24 +9457,24 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
@@ -9491,16 +9499,16 @@
         <v>147</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9510,7 +9518,7 @@
         <v>77</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>77</v>
@@ -9549,7 +9557,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9567,21 +9575,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9690,10 +9698,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9804,10 +9812,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9833,16 +9841,16 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9891,7 +9899,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9909,21 +9917,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9949,13 +9957,13 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10005,7 +10013,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10023,21 +10031,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10063,14 +10071,14 @@
         <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10119,7 +10127,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10137,21 +10145,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10177,16 +10185,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10235,7 +10243,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10253,21 +10261,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10290,19 +10298,19 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10351,7 +10359,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10369,24 +10377,24 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>77</v>
@@ -10411,16 +10419,16 @@
         <v>147</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10430,7 +10438,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -10469,7 +10477,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10487,21 +10495,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10610,10 +10618,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10724,10 +10732,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10753,16 +10761,16 @@
         <v>129</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10811,7 +10819,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10829,21 +10837,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10869,13 +10877,13 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10925,7 +10933,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10943,21 +10951,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10983,14 +10991,14 @@
         <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11039,7 +11047,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11057,21 +11065,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11097,16 +11105,16 @@
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11155,7 +11163,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11173,21 +11181,21 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11210,19 +11218,19 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11271,7 +11279,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11289,24 +11297,24 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>77</v>
@@ -11331,16 +11339,16 @@
         <v>147</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -11350,7 +11358,7 @@
         <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>77</v>
@@ -11389,7 +11397,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11407,21 +11415,21 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11530,10 +11538,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11644,10 +11652,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11673,16 +11681,16 @@
         <v>129</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11731,7 +11739,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11749,21 +11757,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11789,13 +11797,13 @@
         <v>101</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11845,7 +11853,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11863,21 +11871,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11903,14 +11911,14 @@
         <v>172</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11959,7 +11967,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11977,21 +11985,21 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12017,16 +12025,16 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12075,7 +12083,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12093,21 +12101,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12130,19 +12138,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12191,7 +12199,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12209,21 +12217,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12249,16 +12257,16 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12307,7 +12315,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12325,21 +12333,21 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12365,13 +12373,13 @@
         <v>172</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12397,13 +12405,13 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>77</v>
@@ -12421,7 +12429,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12439,7 +12447,7 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -12450,10 +12458,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12476,16 +12484,16 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12535,7 +12543,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12547,27 +12555,27 @@
         <v>155</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12676,10 +12684,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12790,10 +12798,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12819,13 +12827,13 @@
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12875,7 +12883,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12884,7 +12892,7 @@
         <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>99</v>
@@ -12893,7 +12901,7 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12904,10 +12912,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12933,13 +12941,13 @@
         <v>129</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12968,10 +12976,10 @@
         <v>151</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>77</v>
@@ -12989,7 +12997,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13007,7 +13015,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13018,10 +13026,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13044,16 +13052,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13103,7 +13111,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13121,21 +13129,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13161,13 +13169,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13217,7 +13225,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13235,7 +13243,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -13246,10 +13254,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13272,16 +13280,16 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13310,10 +13318,10 @@
         <v>162</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13331,7 +13339,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13346,24 +13354,24 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13472,10 +13480,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13586,10 +13594,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13615,16 +13623,16 @@
         <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13671,7 +13679,7 @@
         <v>114</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13689,24 +13697,24 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="B98" t="s" s="2">
-        <v>470</v>
-      </c>
       <c r="C98" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
@@ -13731,16 +13739,16 @@
         <v>147</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13750,7 +13758,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13765,11 +13773,11 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -13787,7 +13795,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13805,21 +13813,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13928,10 +13936,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14042,10 +14050,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14071,16 +14079,16 @@
         <v>129</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -14129,7 +14137,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14147,21 +14155,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14187,13 +14195,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14243,7 +14251,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14261,21 +14269,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14301,14 +14309,14 @@
         <v>172</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14357,7 +14365,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14375,21 +14383,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14415,16 +14423,16 @@
         <v>101</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14473,7 +14481,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14491,21 +14499,21 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14528,19 +14536,19 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14589,7 +14597,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14607,21 +14615,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14647,16 +14655,16 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -14705,7 +14713,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14723,21 +14731,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14760,16 +14768,16 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14819,7 +14827,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14831,27 +14839,27 @@
         <v>155</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14960,10 +14968,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15074,10 +15082,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15100,16 +15108,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15139,7 +15147,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
@@ -15157,7 +15165,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15169,27 +15177,27 @@
         <v>155</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15298,10 +15306,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15412,13 +15420,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="B113" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="C113" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -15440,13 +15448,13 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15506,7 +15514,7 @@
         <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>116</v>
@@ -15515,7 +15523,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15526,10 +15534,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15638,10 +15646,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15667,10 +15675,10 @@
         <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15750,10 +15758,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15779,13 +15787,13 @@
         <v>129</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15793,7 +15801,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>77</v>
@@ -15835,7 +15843,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>87</v>
@@ -15853,7 +15861,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15864,10 +15872,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15893,10 +15901,10 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15920,7 +15928,7 @@
         <v>77</v>
       </c>
       <c r="W117" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="X117" t="s" s="2">
         <v>77</v>
@@ -15947,7 +15955,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15965,7 +15973,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15976,13 +15984,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -16004,13 +16012,13 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16070,7 +16078,7 @@
         <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>116</v>
@@ -16079,7 +16087,7 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
@@ -16090,10 +16098,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16202,10 +16210,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16231,10 +16239,10 @@
         <v>108</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16314,10 +16322,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16343,13 +16351,13 @@
         <v>129</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16357,7 +16365,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>77</v>
@@ -16399,7 +16407,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16417,7 +16425,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16428,10 +16436,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16457,10 +16465,10 @@
         <v>101</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16484,7 +16492,7 @@
         <v>77</v>
       </c>
       <c r="W122" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="X122" t="s" s="2">
         <v>77</v>
@@ -16511,7 +16519,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16529,7 +16537,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16540,10 +16548,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16566,19 +16574,19 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16627,7 +16635,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16636,7 +16644,7 @@
         <v>87</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>99</v>
@@ -16645,21 +16653,21 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16685,20 +16693,20 @@
         <v>172</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q124" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="R124" t="s" s="2">
         <v>77</v>
@@ -16719,13 +16727,13 @@
         <v>77</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>77</v>
@@ -16743,7 +16751,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16761,21 +16769,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16801,16 +16809,16 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16859,7 +16867,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16877,21 +16885,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16917,16 +16925,16 @@
         <v>129</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16975,7 +16983,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16984,7 +16992,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -16993,21 +17001,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17033,16 +17041,16 @@
         <v>172</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17091,7 +17099,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17109,21 +17117,21 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17146,16 +17154,16 @@
         <v>88</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17185,7 +17193,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>77</v>
@@ -17203,7 +17211,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17215,27 +17223,27 @@
         <v>155</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17344,10 +17352,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17458,10 +17466,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17484,19 +17492,19 @@
         <v>88</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -17545,7 +17553,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17554,7 +17562,7 @@
         <v>87</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
@@ -17563,21 +17571,21 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17603,20 +17611,20 @@
         <v>172</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q132" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="R132" t="s" s="2">
         <v>77</v>
@@ -17637,13 +17645,13 @@
         <v>77</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -17661,7 +17669,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17679,21 +17687,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17719,16 +17727,16 @@
         <v>101</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -17777,7 +17785,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17795,21 +17803,21 @@
         <v>77</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17835,16 +17843,16 @@
         <v>129</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -17893,7 +17901,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17902,7 +17910,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -17911,21 +17919,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17951,16 +17959,16 @@
         <v>172</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -18009,7 +18017,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18027,21 +18035,21 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18064,16 +18072,16 @@
         <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18123,7 +18131,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18141,7 +18149,7 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
@@ -18152,10 +18160,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18264,10 +18272,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18378,13 +18386,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B139" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="B139" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="C139" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>77</v>
@@ -18406,13 +18414,13 @@
         <v>77</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18472,7 +18480,7 @@
         <v>79</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>116</v>
@@ -18481,7 +18489,7 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
@@ -18492,14 +18500,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18521,16 +18529,16 @@
         <v>108</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18579,7 +18587,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18597,7 +18605,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18608,10 +18616,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18634,17 +18642,17 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18681,7 +18689,7 @@
         <v>77</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -18691,7 +18699,7 @@
         <v>141</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>87</v>
@@ -18706,27 +18714,27 @@
         <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>77</v>
@@ -18748,17 +18756,17 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18807,7 +18815,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>87</v>
@@ -18822,24 +18830,24 @@
         <v>99</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18948,10 +18956,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19062,10 +19070,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19091,16 +19099,16 @@
         <v>147</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -19147,7 +19155,7 @@
         <v>114</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19165,24 +19173,24 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="B146" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="C146" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>77</v>
@@ -19207,16 +19215,16 @@
         <v>147</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>77</v>
@@ -19226,7 +19234,7 @@
         <v>77</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>77</v>
@@ -19265,7 +19273,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19283,21 +19291,21 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM146" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19406,10 +19414,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19520,10 +19528,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19549,16 +19557,16 @@
         <v>129</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -19607,7 +19615,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19625,21 +19633,21 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19665,13 +19673,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19721,7 +19729,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19739,21 +19747,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19779,14 +19787,14 @@
         <v>172</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19835,7 +19843,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19853,21 +19861,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19893,16 +19901,16 @@
         <v>101</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19951,7 +19959,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19969,21 +19977,21 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20006,19 +20014,19 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -20067,7 +20075,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20085,24 +20093,24 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>77</v>
@@ -20127,16 +20135,16 @@
         <v>147</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -20146,7 +20154,7 @@
         <v>77</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>77</v>
@@ -20185,7 +20193,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20203,21 +20211,21 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20326,10 +20334,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20440,10 +20448,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20469,16 +20477,16 @@
         <v>129</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>77</v>
@@ -20527,7 +20535,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20545,21 +20553,21 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20585,13 +20593,13 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -20641,7 +20649,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20659,21 +20667,21 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20699,14 +20707,14 @@
         <v>172</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>77</v>
@@ -20755,7 +20763,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20773,21 +20781,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20813,16 +20821,16 @@
         <v>101</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20871,7 +20879,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20889,21 +20897,21 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20926,19 +20934,19 @@
         <v>88</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -20987,7 +20995,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21005,24 +21013,24 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>77</v>
@@ -21047,16 +21055,16 @@
         <v>147</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -21066,7 +21074,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -21105,7 +21113,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21123,21 +21131,21 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21246,10 +21254,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21360,10 +21368,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21389,16 +21397,16 @@
         <v>129</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21447,7 +21455,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21465,21 +21473,21 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21505,13 +21513,13 @@
         <v>101</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -21561,7 +21569,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21579,21 +21587,21 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21619,14 +21627,14 @@
         <v>172</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -21675,7 +21683,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21693,21 +21701,21 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21733,16 +21741,16 @@
         <v>101</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21791,7 +21799,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21809,21 +21817,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21846,19 +21854,19 @@
         <v>88</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21907,7 +21915,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21925,21 +21933,21 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21965,16 +21973,16 @@
         <v>101</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22023,7 +22031,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22041,24 +22049,24 @@
         <v>77</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>77</v>
@@ -22080,19 +22088,19 @@
         <v>77</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22141,7 +22149,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -22156,24 +22164,24 @@
         <v>99</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22196,17 +22204,17 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>77</v>
@@ -22255,7 +22263,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22273,7 +22281,7 @@
         <v>77</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
@@ -22284,10 +22292,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22310,16 +22318,16 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -22369,7 +22377,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22381,27 +22389,27 @@
         <v>155</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22510,10 +22518,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22624,13 +22632,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="B176" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="C176" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>77</v>
@@ -22652,13 +22660,13 @@
         <v>77</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22718,7 +22726,7 @@
         <v>79</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>116</v>
@@ -22727,7 +22735,7 @@
         <v>77</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>77</v>
@@ -22738,10 +22746,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22850,10 +22858,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22879,10 +22887,10 @@
         <v>108</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -22962,10 +22970,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22991,13 +22999,13 @@
         <v>129</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -23005,7 +23013,7 @@
       </c>
       <c r="Q179" s="2"/>
       <c r="R179" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="S179" t="s" s="2">
         <v>77</v>
@@ -23047,7 +23055,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>87</v>
@@ -23065,7 +23073,7 @@
         <v>77</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>77</v>
@@ -23076,10 +23084,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23105,10 +23113,10 @@
         <v>101</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -23132,7 +23140,7 @@
         <v>77</v>
       </c>
       <c r="W180" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="X180" t="s" s="2">
         <v>77</v>
@@ -23159,7 +23167,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23177,7 +23185,7 @@
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
@@ -23188,10 +23196,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23214,16 +23222,16 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -23253,7 +23261,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>77</v>
@@ -23271,7 +23279,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23283,27 +23291,27 @@
         <v>155</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23412,10 +23420,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23526,10 +23534,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23552,19 +23560,19 @@
         <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
@@ -23613,7 +23621,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -23622,7 +23630,7 @@
         <v>87</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>99</v>
@@ -23631,21 +23639,21 @@
         <v>77</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23671,20 +23679,20 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q185" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="R185" t="s" s="2">
         <v>77</v>
@@ -23705,13 +23713,13 @@
         <v>77</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>77</v>
@@ -23729,7 +23737,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23747,21 +23755,21 @@
         <v>77</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23787,16 +23795,16 @@
         <v>101</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -23845,7 +23853,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -23863,21 +23871,21 @@
         <v>77</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23903,16 +23911,16 @@
         <v>129</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
@@ -23961,7 +23969,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -23970,7 +23978,7 @@
         <v>87</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>99</v>
@@ -23979,21 +23987,21 @@
         <v>77</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24019,16 +24027,16 @@
         <v>172</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>77</v>
@@ -24077,7 +24085,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24095,21 +24103,21 @@
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24132,16 +24140,16 @@
         <v>88</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -24171,7 +24179,7 @@
       </c>
       <c r="Y189" s="2"/>
       <c r="Z189" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>77</v>
@@ -24189,7 +24197,7 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
@@ -24201,27 +24209,27 @@
         <v>155</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24330,10 +24338,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24444,10 +24452,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24470,19 +24478,19 @@
         <v>88</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>77</v>
@@ -24531,7 +24539,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24540,7 +24548,7 @@
         <v>87</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>99</v>
@@ -24549,21 +24557,21 @@
         <v>77</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24589,20 +24597,20 @@
         <v>172</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q193" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="R193" t="s" s="2">
         <v>77</v>
@@ -24623,13 +24631,13 @@
         <v>77</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>77</v>
@@ -24647,7 +24655,7 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24665,21 +24673,21 @@
         <v>77</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24705,16 +24713,16 @@
         <v>101</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
@@ -24763,7 +24771,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24781,21 +24789,21 @@
         <v>77</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24821,16 +24829,16 @@
         <v>129</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>77</v>
@@ -24879,7 +24887,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -24888,7 +24896,7 @@
         <v>87</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>99</v>
@@ -24897,21 +24905,21 @@
         <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24937,16 +24945,16 @@
         <v>172</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
@@ -24995,7 +25003,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25013,21 +25021,21 @@
         <v>77</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25050,13 +25058,13 @@
         <v>77</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -25107,7 +25115,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25122,10 +25130,10 @@
         <v>99</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>77</v>
@@ -25136,10 +25144,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25248,10 +25256,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25362,14 +25370,14 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -25391,16 +25399,16 @@
         <v>108</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>77</v>
@@ -25449,7 +25457,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25467,7 +25475,7 @@
         <v>77</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>77</v>
@@ -25478,10 +25486,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25507,13 +25515,13 @@
         <v>101</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -25563,7 +25571,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25578,24 +25586,24 @@
         <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25618,13 +25626,13 @@
         <v>77</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -25675,7 +25683,7 @@
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -25690,16 +25698,16 @@
         <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AM202" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7328" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7326" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -499,7 +499,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -533,7 +533,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -576,7 +576,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -611,10 +611,6 @@
     <t>Medication.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -631,16 +627,16 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>Medication.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Medication.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -667,9 +663,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-id-vaccine-extension}
 </t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>Indicator of whether this is a vaccine.</t>
@@ -923,6 +916,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
@@ -1082,10 +1078,10 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>Business identifier for this medication</t>
+  </si>
+  <si>
+    <t>Business identifier for this medication.</t>
   </si>
   <si>
     <t>The serial number could be included as an identifier.</t>
@@ -1130,7 +1126,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1350,7 +1346,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1420,7 +1416,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1477,7 +1473,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1927,7 +1923,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -2606,7 +2602,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4481,7 +4477,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4500,16 +4496,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4559,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4574,10 +4570,10 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4588,10 +4584,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4620,7 +4616,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -4673,7 +4669,7 @@
         <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4691,7 +4687,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4702,16 +4698,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="D19" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4730,17 +4726,15 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4789,7 +4783,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4798,7 +4792,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4807,7 +4801,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4818,13 +4812,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4846,13 +4840,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4903,7 +4897,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4912,7 +4906,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -4921,7 +4915,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4932,10 +4926,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5044,10 +5038,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5073,10 +5067,10 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5156,10 +5150,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5185,13 +5179,13 @@
         <v>129</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5199,7 +5193,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>77</v>
@@ -5241,7 +5235,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -5259,7 +5253,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -5270,10 +5264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5296,13 +5290,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5353,7 +5347,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5371,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -5382,13 +5376,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>77</v>
@@ -5410,13 +5404,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5467,7 +5461,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5476,7 +5470,7 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>116</v>
@@ -5485,7 +5479,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5496,10 +5490,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5608,10 +5602,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5637,10 +5631,10 @@
         <v>108</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5720,10 +5714,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5749,13 +5743,13 @@
         <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5763,7 +5757,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
@@ -5805,7 +5799,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>87</v>
@@ -5823,7 +5817,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5834,10 +5828,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5863,10 +5857,10 @@
         <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5893,11 +5887,11 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5915,7 +5909,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5933,7 +5927,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5944,10 +5938,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6056,10 +6050,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6170,10 +6164,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6199,16 +6193,16 @@
         <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6257,7 +6251,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6275,21 +6269,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6315,13 +6309,13 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6371,7 +6365,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6389,21 +6383,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6429,14 +6423,14 @@
         <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6485,7 +6479,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6503,21 +6497,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6543,16 +6537,16 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6601,7 +6595,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6619,21 +6613,21 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6656,19 +6650,19 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6717,7 +6711,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6735,24 +6729,24 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6774,13 +6768,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6831,7 +6825,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6840,7 +6834,7 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>116</v>
@@ -6849,7 +6843,7 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6860,10 +6854,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6972,10 +6966,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7086,10 +7080,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7115,13 +7109,13 @@
         <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -7129,7 +7123,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
@@ -7171,7 +7165,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>87</v>
@@ -7189,7 +7183,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7200,10 +7194,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7229,10 +7223,10 @@
         <v>172</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7259,11 +7253,11 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -7281,7 +7275,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7299,7 +7293,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -7310,13 +7304,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>77</v>
@@ -7338,13 +7332,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7395,7 +7389,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7404,7 +7398,7 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>116</v>
@@ -7413,7 +7407,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7424,10 +7418,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7536,10 +7530,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7565,10 +7559,10 @@
         <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7648,10 +7642,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7677,13 +7671,13 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7691,7 +7685,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>77</v>
@@ -7733,7 +7727,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7751,7 +7745,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7762,10 +7756,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7791,10 +7785,10 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7818,7 +7812,7 @@
         <v>77</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="X46" t="s" s="2">
         <v>77</v>
@@ -7845,7 +7839,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7863,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7874,13 +7868,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7902,13 +7896,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7959,7 +7953,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7968,7 +7962,7 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>116</v>
@@ -7977,7 +7971,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7988,10 +7982,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8100,10 +8094,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8129,10 +8123,10 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8212,10 +8206,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8241,13 +8235,13 @@
         <v>129</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8255,7 +8249,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>77</v>
@@ -8297,7 +8291,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>87</v>
@@ -8315,7 +8309,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8326,10 +8320,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8355,10 +8349,10 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8382,7 +8376,7 @@
         <v>77</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="X51" t="s" s="2">
         <v>77</v>
@@ -8409,7 +8403,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8427,7 +8421,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8438,16 +8432,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>321</v>
-      </c>
       <c r="D52" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8466,17 +8460,15 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8525,7 +8517,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8534,7 +8526,7 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>116</v>
@@ -8543,7 +8535,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8554,10 +8546,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8583,16 +8575,16 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8641,7 +8633,7 @@
         <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8659,7 +8651,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8670,10 +8662,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8696,16 +8688,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8753,7 +8745,7 @@
         <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8771,24 +8763,24 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8810,16 +8802,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8830,7 +8822,7 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>77</v>
@@ -8869,7 +8861,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8887,24 +8879,24 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8926,16 +8918,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8946,7 +8938,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8985,7 +8977,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9003,21 +8995,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9040,16 +9032,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9078,11 +9070,11 @@
         <v>162</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
       </c>
@@ -9099,7 +9091,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9114,24 +9106,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9240,10 +9232,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9354,10 +9346,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9383,16 +9375,16 @@
         <v>147</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9439,7 +9431,7 @@
         <v>114</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9457,24 +9449,24 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>77</v>
@@ -9499,16 +9491,16 @@
         <v>147</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9518,7 +9510,7 @@
         <v>77</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>77</v>
@@ -9557,7 +9549,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9575,21 +9567,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9698,10 +9690,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9812,10 +9804,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9841,16 +9833,16 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9899,7 +9891,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9917,21 +9909,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9957,13 +9949,13 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10013,7 +10005,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10031,21 +10023,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10071,14 +10063,14 @@
         <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10127,7 +10119,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10145,21 +10137,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10185,16 +10177,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10243,7 +10235,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10261,21 +10253,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10298,19 +10290,19 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10359,7 +10351,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10377,24 +10369,24 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>77</v>
@@ -10419,16 +10411,16 @@
         <v>147</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10438,7 +10430,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -10477,7 +10469,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10495,21 +10487,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10618,10 +10610,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10732,10 +10724,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10761,16 +10753,16 @@
         <v>129</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10819,7 +10811,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10837,21 +10829,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10877,13 +10869,13 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10933,7 +10925,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10951,21 +10943,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10991,14 +10983,14 @@
         <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11047,7 +11039,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11065,21 +11057,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11105,16 +11097,16 @@
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11163,7 +11155,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11181,21 +11173,21 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11218,19 +11210,19 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11279,7 +11271,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11297,24 +11289,24 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>77</v>
@@ -11339,16 +11331,16 @@
         <v>147</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -11358,7 +11350,7 @@
         <v>77</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>77</v>
@@ -11397,7 +11389,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11415,21 +11407,21 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11538,10 +11530,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11652,10 +11644,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11681,16 +11673,16 @@
         <v>129</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11739,7 +11731,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11757,21 +11749,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11797,13 +11789,13 @@
         <v>101</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11853,7 +11845,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11871,21 +11863,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11911,14 +11903,14 @@
         <v>172</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11967,7 +11959,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11985,21 +11977,21 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12025,16 +12017,16 @@
         <v>101</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12083,7 +12075,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12101,21 +12093,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12138,19 +12130,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12199,7 +12191,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12217,21 +12209,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12257,16 +12249,16 @@
         <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12315,7 +12307,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12333,21 +12325,21 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12373,13 +12365,13 @@
         <v>172</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12405,14 +12397,14 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>422</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12429,7 +12421,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12447,7 +12439,7 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -12458,10 +12450,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12484,16 +12476,16 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12543,7 +12535,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12555,27 +12547,27 @@
         <v>155</v>
       </c>
       <c r="AJ87" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AK87" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AK87" t="s" s="2">
+      <c r="AL87" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AM87" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>433</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12684,10 +12676,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12798,10 +12790,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12827,13 +12819,13 @@
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12883,16 +12875,16 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>99</v>
@@ -12901,7 +12893,7 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12912,10 +12904,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12941,13 +12933,13 @@
         <v>129</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12976,28 +12968,28 @@
         <v>151</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z91" t="s" s="2">
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13015,7 +13007,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13026,10 +13018,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13052,16 +13044,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13111,7 +13103,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13129,21 +13121,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13169,13 +13161,13 @@
         <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13225,7 +13217,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13243,7 +13235,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -13254,10 +13246,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13280,16 +13272,16 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13318,11 +13310,11 @@
         <v>162</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
       </c>
@@ -13339,7 +13331,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13354,24 +13346,24 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL94" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AM94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13480,10 +13472,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13594,10 +13586,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13623,16 +13615,16 @@
         <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13679,7 +13671,7 @@
         <v>114</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13697,24 +13689,24 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
@@ -13739,16 +13731,16 @@
         <v>147</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M98" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="N98" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13758,7 +13750,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13773,11 +13765,11 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -13795,7 +13787,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13813,21 +13805,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13936,10 +13928,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14050,10 +14042,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14079,16 +14071,16 @@
         <v>129</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -14137,7 +14129,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14155,21 +14147,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14195,13 +14187,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N102" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14251,7 +14243,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14269,21 +14261,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14309,14 +14301,14 @@
         <v>172</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14365,7 +14357,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14383,21 +14375,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14423,16 +14415,16 @@
         <v>101</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14481,7 +14473,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14499,21 +14491,21 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14536,19 +14528,19 @@
         <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14597,7 +14589,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14615,21 +14607,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14655,16 +14647,16 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -14713,7 +14705,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14731,21 +14723,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14768,16 +14760,16 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14827,7 +14819,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14839,27 +14831,27 @@
         <v>155</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AK107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14968,10 +14960,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15082,10 +15074,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15108,16 +15100,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15147,25 +15139,25 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15177,27 +15169,27 @@
         <v>155</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL110" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL110" t="s" s="2">
+      <c r="AM110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN110" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15306,10 +15298,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15420,13 +15412,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -15448,13 +15440,13 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15514,7 +15506,7 @@
         <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>116</v>
@@ -15523,7 +15515,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15534,10 +15526,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15646,10 +15638,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15675,10 +15667,10 @@
         <v>108</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15758,10 +15750,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15787,13 +15779,13 @@
         <v>129</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15801,7 +15793,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>77</v>
@@ -15843,7 +15835,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>87</v>
@@ -15861,7 +15853,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15872,10 +15864,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15901,10 +15893,10 @@
         <v>101</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15928,7 +15920,7 @@
         <v>77</v>
       </c>
       <c r="W117" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="X117" t="s" s="2">
         <v>77</v>
@@ -15955,7 +15947,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -15973,7 +15965,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15984,13 +15976,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -16012,13 +16004,13 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16078,7 +16070,7 @@
         <v>79</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>116</v>
@@ -16087,7 +16079,7 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
@@ -16098,10 +16090,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16210,10 +16202,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16239,10 +16231,10 @@
         <v>108</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16322,10 +16314,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16351,13 +16343,13 @@
         <v>129</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N121" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16365,7 +16357,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>77</v>
@@ -16407,7 +16399,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16425,7 +16417,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16436,10 +16428,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16465,10 +16457,10 @@
         <v>101</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16492,7 +16484,7 @@
         <v>77</v>
       </c>
       <c r="W122" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="X122" t="s" s="2">
         <v>77</v>
@@ -16519,7 +16511,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16537,7 +16529,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16548,10 +16540,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16574,19 +16566,19 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N123" t="s" s="2">
+      <c r="O123" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16635,7 +16627,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16644,7 +16636,7 @@
         <v>87</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
         <v>99</v>
@@ -16653,21 +16645,21 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16693,65 +16685,65 @@
         <v>172</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q124" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="P124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q124" t="s" s="2">
+      <c r="R124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y124" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="R124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y124" t="s" s="2">
+      <c r="Z124" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z124" t="s" s="2">
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16769,21 +16761,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16809,16 +16801,16 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O125" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16867,7 +16859,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16885,21 +16877,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16925,16 +16917,16 @@
         <v>129</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16983,16 +16975,16 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI126" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -17001,21 +16993,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17041,16 +17033,16 @@
         <v>172</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17099,7 +17091,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17117,21 +17109,21 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17154,16 +17146,16 @@
         <v>88</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="N128" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17193,7 +17185,7 @@
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>77</v>
@@ -17211,7 +17203,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17223,27 +17215,27 @@
         <v>155</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17352,10 +17344,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17466,10 +17458,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17492,19 +17484,19 @@
         <v>88</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -17553,7 +17545,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17562,7 +17554,7 @@
         <v>87</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>99</v>
@@ -17571,21 +17563,21 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17611,65 +17603,65 @@
         <v>172</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q132" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="P132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q132" t="s" s="2">
+      <c r="R132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y132" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="R132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y132" t="s" s="2">
+      <c r="Z132" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z132" t="s" s="2">
+      <c r="AA132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF132" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17687,21 +17679,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17727,16 +17719,16 @@
         <v>101</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O133" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -17785,7 +17777,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17803,21 +17795,21 @@
         <v>77</v>
       </c>
       <c r="AL133" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN133" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17843,16 +17835,16 @@
         <v>129</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -17901,16 +17893,16 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI134" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -17919,21 +17911,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17959,16 +17951,16 @@
         <v>172</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -18017,7 +18009,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18035,21 +18027,21 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18072,16 +18064,16 @@
         <v>77</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18131,7 +18123,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18149,7 +18141,7 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>77</v>
@@ -18160,10 +18152,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18272,10 +18264,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18386,13 +18378,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>77</v>
@@ -18414,13 +18406,13 @@
         <v>77</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18480,7 +18472,7 @@
         <v>79</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>116</v>
@@ -18489,7 +18481,7 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
@@ -18500,14 +18492,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18529,16 +18521,16 @@
         <v>108</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18587,7 +18579,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18605,7 +18597,7 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
@@ -18616,10 +18608,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18642,17 +18634,17 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18689,7 +18681,7 @@
         <v>77</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AC141" s="2"/>
       <c r="AD141" t="s" s="2">
@@ -18699,7 +18691,7 @@
         <v>141</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>87</v>
@@ -18714,27 +18706,27 @@
         <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C142" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>77</v>
@@ -18756,17 +18748,17 @@
         <v>77</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18815,7 +18807,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>87</v>
@@ -18830,24 +18822,24 @@
         <v>99</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18956,10 +18948,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19070,10 +19062,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B145" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19099,16 +19091,16 @@
         <v>147</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -19155,7 +19147,7 @@
         <v>114</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19173,24 +19165,24 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>77</v>
@@ -19215,16 +19207,16 @@
         <v>147</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>77</v>
@@ -19234,7 +19226,7 @@
         <v>77</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>77</v>
@@ -19273,7 +19265,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19291,21 +19283,21 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN146" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19414,10 +19406,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19528,10 +19520,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B149" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19557,16 +19549,16 @@
         <v>129</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -19615,7 +19607,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19633,21 +19625,21 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B150" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19673,13 +19665,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19729,7 +19721,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19747,21 +19739,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B151" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19787,14 +19779,14 @@
         <v>172</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19843,7 +19835,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19861,21 +19853,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19901,16 +19893,16 @@
         <v>101</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19959,7 +19951,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19977,21 +19969,21 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B153" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20014,19 +20006,19 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -20075,7 +20067,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20093,24 +20085,24 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D154" t="s" s="2">
         <v>77</v>
@@ -20135,16 +20127,16 @@
         <v>147</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -20154,7 +20146,7 @@
         <v>77</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>77</v>
@@ -20193,7 +20185,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -20211,21 +20203,21 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20334,10 +20326,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20448,10 +20440,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20477,16 +20469,16 @@
         <v>129</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>77</v>
@@ -20535,7 +20527,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20553,21 +20545,21 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20593,13 +20585,13 @@
         <v>101</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -20649,7 +20641,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20667,21 +20659,21 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20707,14 +20699,14 @@
         <v>172</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>77</v>
@@ -20763,7 +20755,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20781,21 +20773,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20821,16 +20813,16 @@
         <v>101</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20879,7 +20871,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20897,21 +20889,21 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20934,19 +20926,19 @@
         <v>88</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -20995,7 +20987,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21013,24 +21005,24 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>77</v>
@@ -21055,16 +21047,16 @@
         <v>147</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -21074,7 +21066,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -21113,7 +21105,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21131,21 +21123,21 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN162" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN162" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21254,10 +21246,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21368,10 +21360,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21397,16 +21389,16 @@
         <v>129</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21455,7 +21447,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21473,21 +21465,21 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21513,13 +21505,13 @@
         <v>101</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -21569,7 +21561,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21587,21 +21579,21 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21627,14 +21619,14 @@
         <v>172</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -21683,7 +21675,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21701,21 +21693,21 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21741,16 +21733,16 @@
         <v>101</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21799,7 +21791,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21817,21 +21809,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21854,19 +21846,19 @@
         <v>88</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21915,7 +21907,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21933,21 +21925,21 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B170" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21973,16 +21965,16 @@
         <v>101</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="N170" t="s" s="2">
+      <c r="O170" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22031,7 +22023,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22049,24 +22041,24 @@
         <v>77</v>
       </c>
       <c r="AL170" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN170" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C171" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>77</v>
@@ -22088,19 +22080,19 @@
         <v>77</v>
       </c>
       <c r="K171" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L171" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="L171" t="s" s="2">
+      <c r="M171" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N171" t="s" s="2">
-        <v>664</v>
-      </c>
       <c r="O171" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22149,7 +22141,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -22164,24 +22156,24 @@
         <v>99</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AL171" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN171" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AM171" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN171" t="s" s="2">
-        <v>615</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22204,17 +22196,17 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>77</v>
@@ -22263,7 +22255,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22281,7 +22273,7 @@
         <v>77</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
@@ -22292,10 +22284,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22318,16 +22310,16 @@
         <v>77</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M173" t="s" s="2">
-        <v>672</v>
-      </c>
       <c r="N173" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -22377,7 +22369,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22389,27 +22381,27 @@
         <v>155</v>
       </c>
       <c r="AJ173" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AL173" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AK173" t="s" s="2">
+      <c r="AM173" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN173" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AL173" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM173" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>674</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22518,10 +22510,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22632,13 +22624,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>77</v>
@@ -22660,13 +22652,13 @@
         <v>77</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22726,7 +22718,7 @@
         <v>79</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>116</v>
@@ -22735,7 +22727,7 @@
         <v>77</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>77</v>
@@ -22746,10 +22738,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22858,10 +22850,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22887,10 +22879,10 @@
         <v>108</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -22970,10 +22962,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22999,13 +22991,13 @@
         <v>129</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -23013,7 +23005,7 @@
       </c>
       <c r="Q179" s="2"/>
       <c r="R179" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="S179" t="s" s="2">
         <v>77</v>
@@ -23055,7 +23047,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>87</v>
@@ -23073,7 +23065,7 @@
         <v>77</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>77</v>
@@ -23084,10 +23076,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B180" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23113,10 +23105,10 @@
         <v>101</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -23140,7 +23132,7 @@
         <v>77</v>
       </c>
       <c r="W180" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="X180" t="s" s="2">
         <v>77</v>
@@ -23167,7 +23159,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23185,7 +23177,7 @@
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
@@ -23196,10 +23188,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23222,16 +23214,16 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L181" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L181" t="s" s="2">
+      <c r="M181" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -23261,25 +23253,25 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF181" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23291,27 +23283,27 @@
         <v>155</v>
       </c>
       <c r="AJ181" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL181" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL181" t="s" s="2">
+      <c r="AM181" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN181" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23420,10 +23412,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23534,10 +23526,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23560,19 +23552,19 @@
         <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M184" t="s" s="2">
+      <c r="N184" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N184" t="s" s="2">
+      <c r="O184" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
@@ -23621,7 +23613,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -23630,7 +23622,7 @@
         <v>87</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>99</v>
@@ -23639,21 +23631,21 @@
         <v>77</v>
       </c>
       <c r="AL184" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN184" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23679,65 +23671,65 @@
         <v>172</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q185" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="P185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q185" t="s" s="2">
+      <c r="R185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y185" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="R185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y185" t="s" s="2">
+      <c r="Z185" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z185" t="s" s="2">
+      <c r="AA185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF185" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23755,21 +23747,21 @@
         <v>77</v>
       </c>
       <c r="AL185" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN185" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23795,16 +23787,16 @@
         <v>101</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O186" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -23853,7 +23845,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -23871,21 +23863,21 @@
         <v>77</v>
       </c>
       <c r="AL186" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN186" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23911,16 +23903,16 @@
         <v>129</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
@@ -23969,16 +23961,16 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI187" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>99</v>
@@ -23987,21 +23979,21 @@
         <v>77</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24027,16 +24019,16 @@
         <v>172</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M188" t="s" s="2">
+      <c r="N188" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N188" t="s" s="2">
+      <c r="O188" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>77</v>
@@ -24085,7 +24077,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24103,21 +24095,21 @@
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24140,16 +24132,16 @@
         <v>88</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L189" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M189" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M189" t="s" s="2">
-        <v>581</v>
-      </c>
       <c r="N189" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
@@ -24179,7 +24171,7 @@
       </c>
       <c r="Y189" s="2"/>
       <c r="Z189" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>77</v>
@@ -24197,7 +24189,7 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>78</v>
@@ -24209,27 +24201,27 @@
         <v>155</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24338,10 +24330,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24452,10 +24444,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24478,19 +24470,19 @@
         <v>88</v>
       </c>
       <c r="K192" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L192" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L192" t="s" s="2">
+      <c r="M192" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M192" t="s" s="2">
+      <c r="N192" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N192" t="s" s="2">
+      <c r="O192" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>77</v>
@@ -24539,7 +24531,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24548,7 +24540,7 @@
         <v>87</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>99</v>
@@ -24557,21 +24549,21 @@
         <v>77</v>
       </c>
       <c r="AL192" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN192" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>546</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24597,65 +24589,65 @@
         <v>172</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q193" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="P193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q193" t="s" s="2">
+      <c r="R193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="Y193" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="R193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y193" t="s" s="2">
+      <c r="Z193" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z193" t="s" s="2">
+      <c r="AA193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF193" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24673,21 +24665,21 @@
         <v>77</v>
       </c>
       <c r="AL193" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN193" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24713,16 +24705,16 @@
         <v>101</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="O194" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
@@ -24771,7 +24763,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24789,21 +24781,21 @@
         <v>77</v>
       </c>
       <c r="AL194" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN194" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24829,16 +24821,16 @@
         <v>129</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N195" t="s" s="2">
+      <c r="O195" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>77</v>
@@ -24887,16 +24879,16 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI195" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>99</v>
@@ -24905,21 +24897,21 @@
         <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24945,16 +24937,16 @@
         <v>172</v>
       </c>
       <c r="L196" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M196" t="s" s="2">
+      <c r="N196" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="N196" t="s" s="2">
+      <c r="O196" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
@@ -25003,7 +24995,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -25021,21 +25013,21 @@
         <v>77</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25058,13 +25050,13 @@
         <v>77</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L197" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -25115,7 +25107,7 @@
         <v>77</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>78</v>
@@ -25130,10 +25122,10 @@
         <v>99</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>77</v>
@@ -25144,10 +25136,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25256,10 +25248,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -25370,14 +25362,14 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -25399,16 +25391,16 @@
         <v>108</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>77</v>
@@ -25457,7 +25449,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25475,7 +25467,7 @@
         <v>77</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>77</v>
@@ -25486,10 +25478,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25515,13 +25507,13 @@
         <v>101</v>
       </c>
       <c r="L201" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="M201" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M201" t="s" s="2">
-        <v>719</v>
-      </c>
       <c r="N201" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
@@ -25571,7 +25563,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25586,24 +25578,24 @@
         <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -25626,13 +25618,13 @@
         <v>77</v>
       </c>
       <c r="K202" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="L202" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="L202" t="s" s="2">
+      <c r="M202" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -25683,7 +25675,7 @@
         <v>77</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>78</v>
@@ -25698,16 +25690,16 @@
         <v>99</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AL202" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="AM202" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN202" t="s" s="2">
         <v>725</v>
-      </c>
-      <c r="AM202" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN202" t="s" s="2">
-        <v>726</v>
       </c>
     </row>
   </sheetData>
